--- a/ig/DM-37/CodeSystem-TRE-R251-FonctionContact.xlsx
+++ b/ig/DM-37/CodeSystem-TRE-R251-FonctionContact.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="102">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="135" uniqueCount="104">
   <si>
     <t>Property</t>
   </si>
@@ -64,7 +64,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-12-15T12:00:00+01:00</t>
+    <t>2024-04-26T12:00:00+01:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -320,6 +320,12 @@
   </si>
   <si>
     <t>Coordonnateur de la gestion des risques associés aux soins</t>
+  </si>
+  <si>
+    <t>27</t>
+  </si>
+  <si>
+    <t>Responsable du Bed Management</t>
   </si>
 </sst>
 </file>
@@ -693,7 +699,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:D27"/>
+  <dimension ref="A1:D28"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -1022,6 +1028,18 @@
       </c>
       <c r="D27" s="2"/>
     </row>
+    <row r="28">
+      <c r="A28" t="s" s="2">
+        <v>49</v>
+      </c>
+      <c r="B28" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="C28" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="D28" s="2"/>
+    </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>
